--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D338"/>
+  <dimension ref="A1:D234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,1748 +441,2296 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AACB</t>
+          <t>ABOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ABXL</t>
+          <t>ACIU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BEEM</t>
+          <t>ABTC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ABTC</t>
+          <t>ARBE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMCI</t>
+          <t>ACCL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACCL</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BTCS</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>ARQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BOSC</t>
+          <t>ACOG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACOG</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>AMOD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ALCO</t>
+          <t>BGIN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BULL</t>
+          <t>ADUR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADAMH</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>ASST</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ASST</t>
+          <t>BTOC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CGEN</t>
+          <t>ADUS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADAMN</t>
+          <t>AEI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>BEEM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ATLX</t>
+          <t>CECO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CSHR</t>
+          <t>AEHL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADIL</t>
+          <t>AIFA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LBRDA</t>
+          <t>BHFAL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>CELZ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ELBM</t>
+          <t>ALM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>AIIR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LBRDK</t>
+          <t>BLSH</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BGIN</t>
+          <t>CENN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBRX</t>
+          <t>ALVO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADPT</t>
+          <t>ALOT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BLSH</t>
+          <t>CRGO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FDSB</t>
+          <t>AMCX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADSK</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>ALXO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BTGO</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BNAI</t>
+          <t>CTOR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FUTU</t>
+          <t>AMLX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ADUS</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>AMPL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CDTG</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BORR</t>
+          <t>ELLA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GLIBA</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AEHL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>AMRX</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DFDV</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BTGO</t>
+          <t>FCFS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IPM</t>
+          <t>ARCT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AEHR</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>ANGX</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EEIQ</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BTOC</t>
+          <t>GLE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JATT</t>
+          <t>ATAI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AEI</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>APGE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ELVR</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CECO</t>
+          <t>GNSS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JCSE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AERT</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>APLM</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EXOZ</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>HAO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MSLE</t>
+          <t>AUGO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AEYE</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GOLD</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CELZ</t>
+          <t>IXHL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NICM</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AIFA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HOLO</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>JSM</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NTRB</t>
+          <t>AXGN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AIIR</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>AREC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ICG</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DOYU</t>
+          <t>JVA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OXLCO</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>ARGX</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>IRD</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DXST</t>
+          <t>KXIN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PMVP</t>
+          <t>BAFN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ALLR</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>ARTNA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>KBSX</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EEIQ</t>
+          <t>LUNR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PRZO</t>
+          <t>BLFS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ALM</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>ARTW</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>KWY</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ELVR</t>
+          <t>MLGO</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PSNL</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ALOT</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>ARX</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LEE</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EXOZ</t>
+          <t>MRAM</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUMS</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ALRM</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>ASBP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LKQ</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FCFS</t>
+          <t>MRM</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SLNHP</t>
+          <t>BOSC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ALXO</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>ATKR</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LOT</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GRSD</t>
+          <t>NEGG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STKH</t>
+          <t>BRNX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AMCX</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>AVBC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MSAI</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HAO</t>
+          <t>NWGL</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BRR</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AMLX</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>AVO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NAKA</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HOLO</t>
+          <t>OPTX</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AMRX</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>AWR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ORBS</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ICON</t>
+          <t>REA</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BULL</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ANGO</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>AXTI</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PHIO</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IPW</t>
+          <t>SMSI</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CABA</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ANGX</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>BBT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PPIH</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ISPC</t>
+          <t>SRZN</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CAI</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>APA</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>BCSS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PRTS</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>VIVO</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CARL</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>APGE</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LEE</t>
-        </is>
-      </c>
+          <t>BEEP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PUSA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>APPF</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LTRX</t>
-        </is>
-      </c>
+          <t>BFRI</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SEV</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CDLR</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LUNR</t>
-        </is>
-      </c>
+          <t>BGDE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SHAZ</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CETY</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ARCC</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>MRAM</t>
-        </is>
-      </c>
+          <t>BIOX</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SPCB</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CFFI</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ARCT</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NAKA</t>
-        </is>
-      </c>
+          <t>BIXI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>STEX</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CGC</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AREC</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ORBS</t>
-        </is>
-      </c>
+          <t>BPYPP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SWVL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CGEN</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ARLP</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>PTN</t>
-        </is>
-      </c>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CHSCO</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ARTW</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>SEV</t>
-        </is>
-      </c>
+          <t>BRLT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TRON</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CJMB</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ASBP</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>SHAZ</t>
-        </is>
-      </c>
+          <t>BSBK</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>USAU</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CLIR</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ATAI</t>
+          <t>BTU</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TLSA</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CLLS</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ATCX</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TMCR</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>COCP</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TRON</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>COHU</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ATLCL</t>
+          <t>BYND</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>USAU</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CORT</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>VMET</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CSTE</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CYPH</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>CDIO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DMLP</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AVO</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DTIL</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DWTX</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ELVN</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AXGN</t>
+          <t>CGAU</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ENTX</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AYA</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EXE</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>FANG</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BAFN</t>
+          <t>CHNR</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FBLG</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BBNX</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>FRHC</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BBT</t>
+          <t>CHTRP</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FUTU</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BCSS</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>FWDI</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BDSX</t>
+          <t>CING</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>GASS</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BEEP</t>
+          <t>CLYM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GH</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BGDE</t>
+          <t>CNOBP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>GLNG</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BIOX</t>
+          <t>CNR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>GNLN</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BIXI</t>
+          <t>CNSP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>GOODO</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BLFS</t>
+          <t>COCH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>GSHD</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>COYA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>HBIO</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>CPBI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>HFBL</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>HMR</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BRR</t>
+          <t>CRBP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>HQI</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BSBK</t>
+          <t>CSAI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>HTHT</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BSIN</t>
+          <t>CSWC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HURN</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BULLW</t>
+          <t>CURI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BWBBP</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>IDYA</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>IMMR</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>DHCNI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IMPP</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CARL</t>
+          <t>DIBS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>INTA</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>DJCO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IOVA</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CBFV</t>
+          <t>DMC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>JATT</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>JCSE</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CDIO</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LEXX</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CDLR</t>
+          <t>DRMA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MAKO</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MANH</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CDTG</t>
+          <t>DTI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MASS</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MEDP</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MEOH</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CETY</t>
+          <t>EDRY</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MESO</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MICC</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CGBD</t>
+          <t>EGHA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MKTX</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MSLE</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>EROK</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NDSN</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>EXFY</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NEPH</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CING</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>NHP</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CLLS</t>
+          <t>FCUV</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NKLR</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CLYM</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NTNX</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>NTRB</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CNOBP</t>
+          <t>FVAV</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>NVCT</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CNR</t>
+          <t>FVN</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>OGC</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CNSP</t>
+          <t>GAINZ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ONBPO</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CNTB</t>
+          <t>GBDC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>OTLY</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>COCP</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OXLCI</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>OXLCO</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>GECC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PAA</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>GLAD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PANL</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CPIX</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PBAM</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CPZ</t>
+          <t>GRRR</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PBHC</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CRBP</t>
+          <t>GTEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PCAP</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CRDL</t>
+          <t>GTIM</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PCYO</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PFX</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CSAI</t>
+          <t>HBANL</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>PGEN</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>PMVP</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CSWC</t>
+          <t>HELP</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>HMH</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>PRPO</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>PRQR</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CYCN</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>PRZO</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>HTO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>PSNL</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>HUDI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>PTGX</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>HWCPZ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>PXS</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DJCO</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>QURE</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>IFRX</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>RDZN</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DRMA</t>
+          <t>IMXI</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>RGEN</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>INBKZ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>RILYN</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DTI</t>
+          <t>IPHA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>RMTI</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DTIL</t>
+          <t>IVDA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>RVMD</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DUKRW</t>
+          <t>JAN</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SATA</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SBET</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>JUNS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SCZM</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ECCU</t>
+          <t>KELYA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SEIC</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>KIDZ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ELVN</t>
+          <t>KLTR</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SLAB</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>KOYN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SMJF</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>KPRX</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SOPH</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>KSPI</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>SRTA</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EROK</t>
+          <t>KZIA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SSRM</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>LARK</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>STKH</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>LEGH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STRD</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>LGVN</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>TLIH</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>FBLG</t>
+          <t>LKSP</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>TLX</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>FCUV</t>
+          <t>LPBB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>TOP</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FGNX</t>
+          <t>LPSN</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>TORO</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FHTX</t>
+          <t>MACI</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>TRLV</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FIEE</t>
+          <t>MBINL</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FIGR</t>
+          <t>MCFT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>YDES</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FORR</t>
+          <t>MCGA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2192,7 +2740,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>MDXH</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2202,7 +2750,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>METCI</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2212,7 +2760,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>MF</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2222,7 +2770,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FVAV</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2232,7 +2780,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2242,7 +2790,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>FWONA</t>
+          <t>MINE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2252,7 +2800,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FWONK</t>
+          <t>MLAA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2262,7 +2810,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GAINI</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2272,7 +2820,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GAME</t>
+          <t>MRDN</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2282,7 +2830,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>GASS</t>
+          <t>MSGY</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2292,7 +2840,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>GBDC</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2302,7 +2850,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2312,7 +2860,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>GECC</t>
+          <t>NEOV</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2322,7 +2870,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>NHPBP</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2332,7 +2880,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GLAD</t>
+          <t>NICM</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2342,7 +2890,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GLNG</t>
+          <t>NMFCZ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2352,7 +2900,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>GMRS</t>
+          <t>NTHI</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2362,7 +2910,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>GNSS</t>
+          <t>NUAI</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2372,7 +2920,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>NWE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2382,7 +2930,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2392,7 +2940,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>GTEC</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2402,7 +2950,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>GTIM</t>
+          <t>NWTG</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2412,7 +2960,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>NXPL</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2422,7 +2970,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>OABI</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2432,7 +2980,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HELP</t>
+          <t>OCSL</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2442,7 +2990,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HMR</t>
+          <t>ODTX</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2452,7 +3000,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>OGG</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2462,7 +3010,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HQY</t>
+          <t>OMER</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2472,7 +3020,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HSLV</t>
+          <t>OMEX</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2482,7 +3030,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>ORKA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2492,7 +3040,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>OXLCM</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2502,7 +3050,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>OXLCZ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2512,7 +3060,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HUDI</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2522,7 +3070,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2532,7 +3080,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2542,7 +3090,7 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>PHOE</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -2552,7 +3100,7 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>PHVS</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -2562,7 +3110,7 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>IDCC</t>
+          <t>PLPC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -2572,7 +3120,7 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>IFRX</t>
+          <t>PLRX</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -2582,7 +3130,7 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>IMXI</t>
+          <t>PLSE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -2592,7 +3140,7 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>INBKZ</t>
+          <t>PMTW</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -2602,7 +3150,7 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>PNRG</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -2612,7 +3160,7 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>INFQ</t>
+          <t>PRAX</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -2622,7 +3170,7 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -2632,7 +3180,7 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>IPHA</t>
+          <t>PRHI</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -2642,7 +3190,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>IVDA</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -2652,7 +3200,7 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>IVVD</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -2662,7 +3210,7 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JAN</t>
+          <t>PTEN</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -2672,7 +3220,7 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JBDI</t>
+          <t>PXLW</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -2682,7 +3230,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>PYPD</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -2692,7 +3240,7 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -2702,7 +3250,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>KRKR</t>
+          <t>RDNT</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -2712,7 +3260,7 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>KRNY</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -2722,7 +3270,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>KSPI</t>
+          <t>RGLD</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -2732,7 +3280,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>KZIA</t>
+          <t>RMNI</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -2742,7 +3290,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>LARK</t>
+          <t>RNXT</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -2752,7 +3300,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -2762,7 +3310,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>LEXX</t>
+          <t>RRGB</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -2772,7 +3320,7 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>RUM</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -2782,7 +3330,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>LGVN</t>
+          <t>RWAYI</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -2792,7 +3340,7 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>LHSW</t>
+          <t>SAIH</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -2802,7 +3350,7 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>LLYVA</t>
+          <t>SBMT</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -2812,7 +3360,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>LLYVK</t>
+          <t>SCYX</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -2822,7 +3370,7 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>LPSN</t>
+          <t>SEGG</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -2832,7 +3380,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>LSE</t>
+          <t>SENEA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -2842,7 +3390,7 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>LUNG</t>
+          <t>SFBC</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -2852,7 +3400,7 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>SHC</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -2862,7 +3410,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MBINL</t>
+          <t>SIEB</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -2872,7 +3420,7 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MCGA</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -2882,7 +3430,7 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>SLMBP</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -2892,7 +3440,7 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MDXH</t>
+          <t>SLP</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -2902,7 +3450,7 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -2912,7 +3460,7 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>SWKHL</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -2922,7 +3470,7 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MESHU</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -2932,7 +3480,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MESO</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -2942,7 +3490,7 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>THH</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -2952,7 +3500,7 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>TLF</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -2962,7 +3510,7 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>MGEE</t>
+          <t>TPCS</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -2972,7 +3520,7 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>MGYR</t>
+          <t>TRIN</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -2982,7 +3530,7 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -2992,7 +3540,7 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>VACI</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -3002,7 +3550,7 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>MMED</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -3012,7 +3560,7 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>MMYT</t>
+          <t>VERU</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -3022,7 +3570,7 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MOB</t>
+          <t>VOXR</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -3032,7 +3580,7 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>MOLN</t>
+          <t>VSECU</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -3042,7 +3590,7 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>WSBCO</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -3052,7 +3600,7 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>MRDN</t>
+          <t>WSTN</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -3062,1051 +3610,11 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>YORW</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr"/>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>MSGY</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr"/>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr"/>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>MYSE</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr"/>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>MYSZ</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr"/>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>NBRG</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr"/>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>NCI</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr"/>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>NDAQ</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr"/>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>NDSN</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr"/>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>NEOV</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr"/>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>NEPH</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr"/>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr"/>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>NHP</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr"/>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>NHPBP</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr"/>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>NNBR</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr"/>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>NTHI</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr"/>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>NTNX</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr"/>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>NTRA</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr"/>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>NUTX</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr"/>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>NWE</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr"/>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr"/>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>NWSA</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr"/>
-      <c r="D254" t="inlineStr"/>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr"/>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>NWTG</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr"/>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr"/>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>NXTT</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr"/>
-      <c r="D256" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr"/>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>OABI</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr"/>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>OMDA</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr"/>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>OMEX</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr"/>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>ONBPO</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr"/>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>ORKA</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr"/>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>OTGA</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr"/>
-      <c r="D262" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr"/>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>OTLY</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr"/>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>OTTR</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr"/>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>OXLCI</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr"/>
-      <c r="D265" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr"/>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>OXLCM</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr"/>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>OZKAP</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr"/>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>PAA</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr"/>
-      <c r="D268" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr"/>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>PAGP</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr"/>
-      <c r="D269" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr"/>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr"/>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>PBAM</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr"/>
-      <c r="D271" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr"/>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>PCTY</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr"/>
-      <c r="D272" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr"/>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>PCYO</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr"/>
-      <c r="D273" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr"/>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>PEPG</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr"/>
-      <c r="D274" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr"/>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>PGEN</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr"/>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>PHVS</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr"/>
-      <c r="D276" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr"/>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>PLPC</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr"/>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>PLRX</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr"/>
-      <c r="D278" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr"/>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>PLSE</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr"/>
-      <c r="D279" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr"/>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>PMTW</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr"/>
-      <c r="D280" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr"/>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>PNRG</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr"/>
-      <c r="D281" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr"/>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>PRCH</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr"/>
-      <c r="D282" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr"/>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>PRHI</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr"/>
-      <c r="D283" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr"/>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>PRLD</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr"/>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>PROV</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr"/>
-      <c r="D285" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr"/>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>PRQR</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr"/>
-      <c r="D286" t="inlineStr"/>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr"/>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr"/>
-      <c r="D287" t="inlineStr"/>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr"/>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>PTGX</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr"/>
-      <c r="D288" t="inlineStr"/>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr"/>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>PXS</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr"/>
-      <c r="D289" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr"/>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>PYPD</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr"/>
-      <c r="D290" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr"/>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr"/>
-      <c r="D291" t="inlineStr"/>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr"/>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>QNCX</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr"/>
-      <c r="D292" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr"/>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>QNST</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr"/>
-      <c r="D293" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr"/>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>QRVO</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr"/>
-      <c r="D294" t="inlineStr"/>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr"/>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>RCMT</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr"/>
-      <c r="D295" t="inlineStr"/>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr"/>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>RCON</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr"/>
-      <c r="D296" t="inlineStr"/>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr"/>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>RDNT</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr"/>
-      <c r="D297" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr"/>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>RDVT</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr"/>
-      <c r="D298" t="inlineStr"/>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr"/>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>RGEN</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr"/>
-      <c r="D299" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr"/>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>RGLD</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr"/>
-      <c r="D300" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr"/>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>RILYN</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr"/>
-      <c r="D301" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr"/>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>RMNI</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr"/>
-      <c r="D302" t="inlineStr"/>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr"/>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>RMTI</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr"/>
-      <c r="D303" t="inlineStr"/>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr"/>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>RVMD</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr"/>
-      <c r="D304" t="inlineStr"/>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr"/>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>RWAYI</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr"/>
-      <c r="D305" t="inlineStr"/>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr"/>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>RWAYL</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr"/>
-      <c r="D306" t="inlineStr"/>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr"/>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>SAIC</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr"/>
-      <c r="D307" t="inlineStr"/>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr"/>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>SAIH</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr"/>
-      <c r="D308" t="inlineStr"/>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr"/>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>SBET</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr"/>
-      <c r="D309" t="inlineStr"/>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr"/>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>SCZM</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr"/>
-      <c r="D310" t="inlineStr"/>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr"/>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>SEIC</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr"/>
-      <c r="D311" t="inlineStr"/>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr"/>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>SFBC</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr"/>
-      <c r="D312" t="inlineStr"/>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr"/>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>SHC</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr"/>
-      <c r="D313" t="inlineStr"/>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr"/>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>SIEB</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr"/>
-      <c r="D314" t="inlineStr"/>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr"/>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>SLAB</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr"/>
-      <c r="D315" t="inlineStr"/>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr"/>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>SLP</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr"/>
-      <c r="D316" t="inlineStr"/>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr"/>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr"/>
-      <c r="D317" t="inlineStr"/>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr"/>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>SRZN</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr"/>
-      <c r="D318" t="inlineStr"/>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr"/>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>SSRM</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr"/>
-      <c r="D319" t="inlineStr"/>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr"/>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>STRC</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr"/>
-      <c r="D320" t="inlineStr"/>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr"/>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>STRD</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr"/>
-      <c r="D321" t="inlineStr"/>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr"/>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr"/>
-      <c r="D322" t="inlineStr"/>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr"/>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>SWKHL</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr"/>
-      <c r="D323" t="inlineStr"/>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr"/>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>SWKS</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr"/>
-      <c r="D324" t="inlineStr"/>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr"/>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>TAYD</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr"/>
-      <c r="D325" t="inlineStr"/>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr"/>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>TBPH</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr"/>
-      <c r="D326" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr"/>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr"/>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>THH</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr"/>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>TLF</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr"/>
-      <c r="D329" t="inlineStr"/>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr"/>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>TOP</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr"/>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>TORO</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr"/>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>TPCS</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr"/>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>TRMD</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr"/>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>VCTR</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr"/>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>VIVO</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr"/>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>WSBCO</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
-      <c r="D336" t="inlineStr"/>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr"/>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>YDES</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr"/>
-      <c r="D337" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr"/>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>YORW</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr"/>
-      <c r="D338" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D234"/>
+  <dimension ref="A1:D425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABOS</t>
+          <t>ABUS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACIU</t>
+          <t>AACG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,2281 +456,1717 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ARBE</t>
+          <t>AD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACCL</t>
+          <t>ASPCU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADIL</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ARQ</t>
+          <t>AEC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACOG</t>
+          <t>ASST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>ABOS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AMOD</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BGIN</t>
+          <t>ATLX</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADUR</t>
+          <t>BRNX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AEHR</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ASST</t>
-        </is>
-      </c>
+          <t>ABXL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BTOC</t>
+          <t>BHFAL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>CBAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AEI</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>BEEM</t>
-        </is>
-      </c>
+          <t>ACCL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CECO</t>
+          <t>BLNK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AEHL</t>
+          <t>CEPO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AIFA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>BHFAL</t>
-        </is>
-      </c>
+          <t>ACFN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CELZ</t>
+          <t>BORR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALM</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AIIR</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>BLSH</t>
-        </is>
-      </c>
+          <t>ACIU</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CENN</t>
+          <t>CD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALVO</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALOT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>BTCS</t>
-        </is>
-      </c>
+          <t>ACOG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRGO</t>
+          <t>CDLX</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMCX</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALXO</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>BTGO</t>
-        </is>
-      </c>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CTOR</t>
+          <t>CDTG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMLX</t>
+          <t>DMAA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMPL</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CDTG</t>
-        </is>
-      </c>
+          <t>ADAG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ELLA</t>
+          <t>CENN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMRX</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>DFDV</t>
-        </is>
-      </c>
+          <t>ADAMH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FCFS</t>
+          <t>CNTY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARCT</t>
+          <t>FUTU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ANGX</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>EEIQ</t>
-        </is>
-      </c>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GLE</t>
+          <t>CPHC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ATAI</t>
+          <t>GECCI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>APGE</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ELVR</t>
-        </is>
-      </c>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GNSS</t>
+          <t>CRGO</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>APLM</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>EXOZ</t>
-        </is>
-      </c>
+          <t>ADUR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HAO</t>
+          <t>DEFT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AUGO</t>
+          <t>HFBL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APPF</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>GOLD</t>
-        </is>
-      </c>
+          <t>ADUS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IXHL</t>
+          <t>DETX</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>HOLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>HOLO</t>
-        </is>
-      </c>
+          <t>AEHL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>DXST</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AXGN</t>
+          <t>JATT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AREC</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ICG</t>
-        </is>
-      </c>
+          <t>AIFA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>ELVR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>JUNS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARGX</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>IRD</t>
-        </is>
-      </c>
+          <t>ALKT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>EVAX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BAFN</t>
+          <t>MSLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ARTNA</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>KBSX</t>
-        </is>
-      </c>
+          <t>ALM</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LUNR</t>
+          <t>EXOZ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BLFS</t>
+          <t>NAKA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ARTW</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>KWY</t>
-        </is>
-      </c>
+          <t>ALVO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MLGO</t>
+          <t>FABC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>NTRB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ARX</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LEE</t>
-        </is>
-      </c>
+          <t>AMCR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MRAM</t>
+          <t>FKWL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>OXLCI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASBP</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LKQ</t>
-        </is>
-      </c>
+          <t>AMCX</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MRM</t>
+          <t>GMTL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BOSC</t>
+          <t>PBHC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ATKR</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>LOT</t>
-        </is>
-      </c>
+          <t>AMLX</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NEGG</t>
+          <t>HAO</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BRNX</t>
+          <t>PCAP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AVBC</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MSAI</t>
-        </is>
-      </c>
+          <t>AMR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NWGL</t>
+          <t>HTZ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BRR</t>
+          <t>TRON</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AVO</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>NAKA</t>
-        </is>
-      </c>
+          <t>AMTX</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OPTX</t>
+          <t>INKT</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>BRZE</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AWR</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ORBS</t>
-        </is>
-      </c>
+          <t>ANGX</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>REA</t>
+          <t>JSM</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>BULL</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AXTI</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>PHIO</t>
-        </is>
-      </c>
+          <t>APGE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
+          <t>JVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>APLM</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JYD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LNZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AQB</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>MLGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AQST</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>OCG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PAHC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ARCC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PPBT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ARCT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PPIH</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ARGX</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PTN</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ARTNA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>QNTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ASBP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ASMB</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ATAI</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SLDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ATKR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>SMSI</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>CABA</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>BBT</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>PPIH</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>SRZN</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>CAI</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BCSS</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>PRTS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>VIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>CARL</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>BEEP</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>PUSA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>CCC</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>BFRI</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SEV</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>CDLR</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>BGDE</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SHAZ</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CETY</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>BIOX</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>SPCB</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>CFFI</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>BIXI</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>STEX</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CGC</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>BPYPP</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ATRC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>SWVL</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>CGEN</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>TEM</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CHSCO</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>BRLT</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>TRON</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>CJMB</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>BSBK</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>USAU</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CLIR</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>BTU</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CLLS</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>BUUU</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>COCP</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>BWIN</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>COHU</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BYND</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TMUS</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>CORT</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>AUGO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>WSE</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CSTE</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>AURA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>CYPH</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>AUTL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>DASH</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CDIO</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>DMLP</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>AVO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>DTIL</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>AVR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>DWTX</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ELVN</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CGAU</t>
+          <t>AXIN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>ENTX</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>AYTU</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>EXE</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>BANX</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>FANG</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>BBIO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>FBLG</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>BCTX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>FRHC</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CHTRP</t>
+          <t>BDTX</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>FUTU</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>BEEM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>FWDI</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CING</t>
+          <t>BEEP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>GASS</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CLYM</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>GH</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CNOBP</t>
+          <t>BGDE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>GLNG</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CNR</t>
+          <t>BIOX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>GNLN</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CNSP</t>
+          <t>BIXI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>GOODO</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>COCH</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>GSHD</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>BLMN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>HBIO</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CPBI</t>
+          <t>BLSH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>HFBL</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>HMR</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CRBP</t>
+          <t>BNTC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>HQI</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CSAI</t>
+          <t>BNTX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>HTHT</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CSWC</t>
+          <t>BOLD</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>HURN</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CURI</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>IA</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>BPYPO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>IDYA</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>IMMR</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DHCNI</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>IMPP</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DIBS</t>
+          <t>BRR</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>INTA</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DJCO</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>IOVA</t>
-        </is>
-      </c>
+      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DMC</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>JATT</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>JCSE</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>BTGO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>LEXX</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DRMA</t>
+          <t>BTU</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>MAKO</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>BUDA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>MANH</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DTI</t>
+          <t>BULL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>MASS</t>
-        </is>
-      </c>
+      <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DUOL</t>
+          <t>BULLW</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>MEDP</t>
-        </is>
-      </c>
+      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>MEOH</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EDRY</t>
+          <t>BVC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>MESO</t>
-        </is>
-      </c>
+      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>MICC</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EGHA</t>
+          <t>BYND</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>MKTX</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>CABA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>MRVL</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>MSLE</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EROK</t>
+          <t>CARL</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>NDAQ</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>NDSN</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EXFY</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>NEPH</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>CCG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>NHP</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FCUV</t>
+          <t>CDLR</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>NKLR</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>NTNX</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>NTRB</t>
-        </is>
-      </c>
+      <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FVAV</t>
+          <t>CELU</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>NVCT</t>
-        </is>
-      </c>
+      <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FVN</t>
+          <t>CGAU</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>OGC</t>
-        </is>
-      </c>
+      <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>CGC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>ONBPO</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GBDC</t>
+          <t>CGEN</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>OTLY</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>OXLCI</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>CHNR</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>OXLCO</t>
-        </is>
-      </c>
+      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GECC</t>
+          <t>CHTRP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>PAA</t>
-        </is>
-      </c>
+      <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GLAD</t>
+          <t>CING</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>PANL</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
+      <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GRDX</t>
+          <t>CLYM</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>PBAM</t>
-        </is>
-      </c>
+      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GRRR</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>PBHC</t>
-        </is>
-      </c>
+      <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GTEC</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>PCAP</t>
-        </is>
-      </c>
+      <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GTIM</t>
+          <t>CMTV</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>PCYO</t>
-        </is>
-      </c>
+      <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>CNET</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>PFX</t>
-        </is>
-      </c>
+      <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>HBANL</t>
+          <t>CNR</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>PGEN</t>
-        </is>
-      </c>
+      <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>COCP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>PMVP</t>
-        </is>
-      </c>
+      <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>HELP</t>
+          <t>CORT</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>PRLD</t>
-        </is>
-      </c>
+      <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HMH</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>PRPO</t>
-        </is>
-      </c>
+      <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>CPBI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>PRQR</t>
-        </is>
-      </c>
+      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>PRZO</t>
-        </is>
-      </c>
+      <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HTO</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>PSNL</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HUDI</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>PTGX</t>
-        </is>
-      </c>
+      <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HWCPZ</t>
+          <t>CSAI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>PXS</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>CSHR</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
+      <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>CSTE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>QURE</t>
-        </is>
-      </c>
+      <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IFRX</t>
+          <t>CSTL</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>RDZN</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IMXI</t>
+          <t>CSWC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>RGEN</t>
-        </is>
-      </c>
+      <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>INBKZ</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>RILYN</t>
-        </is>
-      </c>
+      <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IPHA</t>
+          <t>CTRM</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>RMTI</t>
-        </is>
-      </c>
+      <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IVDA</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>RVMD</t>
-        </is>
-      </c>
+      <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>JAN</t>
+          <t>CYCN</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>SATA</t>
-        </is>
-      </c>
+      <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>DAAQ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>SBET</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JUNS</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>SCZM</t>
-        </is>
-      </c>
+      <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>KELYA</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>SEIC</t>
-        </is>
-      </c>
+      <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>KIDZ</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
+      <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>SLAB</t>
-        </is>
-      </c>
+      <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>KOYN</t>
+          <t>DERM</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>SMJF</t>
-        </is>
-      </c>
+      <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>KPRX</t>
+          <t>DFDV</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>SOPH</t>
-        </is>
-      </c>
+      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>KSPI</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>SRTA</t>
-        </is>
-      </c>
+      <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>KZIA</t>
+          <t>DNMX</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>SSRM</t>
-        </is>
-      </c>
+      <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LARK</t>
+          <t>DNUT</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STKH</t>
-        </is>
-      </c>
+      <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LEGH</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>STRD</t>
-        </is>
-      </c>
+      <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>LGVN</t>
+          <t>DRTS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
+      <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>DRUG</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>TLIH</t>
-        </is>
-      </c>
+      <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LKSP</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>TLX</t>
-        </is>
-      </c>
+      <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LPBB</t>
+          <t>DTIL</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>TOP</t>
-        </is>
-      </c>
+      <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LPSN</t>
+          <t>DWTX</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>TORO</t>
-        </is>
-      </c>
+      <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MACI</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>TRLV</t>
-        </is>
-      </c>
+      <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBINL</t>
+          <t>EDRY</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>TW</t>
-        </is>
-      </c>
+      <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MCFT</t>
+          <t>EEIQ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>YDES</t>
-        </is>
-      </c>
+      <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MCGA</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2740,7 +2176,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MDXH</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2750,7 +2186,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>METCI</t>
+          <t>EGHA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2760,7 +2196,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>ELBM</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2770,7 +2206,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>ELVN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2780,7 +2216,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>ENTX</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2790,7 +2226,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MINE</t>
+          <t>EROK</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2800,7 +2236,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MLAA</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2810,7 +2246,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>EXFY</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2820,7 +2256,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MRDN</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2830,7 +2266,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MSGY</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2840,7 +2276,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>FBLG</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2850,7 +2286,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>FBRX</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2860,7 +2296,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NEOV</t>
+          <t>FCUV</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2870,7 +2306,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NHPBP</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2880,7 +2316,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NICM</t>
+          <t>FHTX</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2890,7 +2326,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NMFCZ</t>
+          <t>FIGR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2900,7 +2336,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>NTHI</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2910,7 +2346,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>NUAI</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2920,7 +2356,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>FLNT</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2930,7 +2366,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2940,7 +2376,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2950,7 +2386,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NWTG</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2960,7 +2396,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2970,7 +2406,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>OABI</t>
+          <t>FOXF</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2980,7 +2416,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>OCSL</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2990,7 +2426,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ODTX</t>
+          <t>FRNM</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -3000,7 +2436,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>OGG</t>
+          <t>FVAV</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -3010,7 +2446,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>OMER</t>
+          <t>FVN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -3020,7 +2456,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>OMEX</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -3030,7 +2466,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ORKA</t>
+          <t>FWONA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3040,7 +2476,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>GAINZ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -3050,7 +2486,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>GASS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -3060,7 +2496,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>GBDC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -3070,7 +2506,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -3080,7 +2516,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -3090,7 +2526,7 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PHOE</t>
+          <t>GECC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -3100,7 +2536,7 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PHVS</t>
+          <t>GECCG</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -3110,7 +2546,7 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PLPC</t>
+          <t>GLBS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -3120,7 +2556,7 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PLRX</t>
+          <t>GLNG</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -3130,7 +2566,7 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PLSE</t>
+          <t>GOLD</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -3140,7 +2576,7 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PMTW</t>
+          <t>GOODO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -3150,7 +2586,7 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -3160,7 +2596,7 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PRAX</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -3170,7 +2606,7 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>GROW</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -3180,7 +2616,7 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>GRRR</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -3190,7 +2626,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>GRVY</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -3200,7 +2636,7 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>GSHD</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -3210,7 +2646,7 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>GTEC</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -3220,7 +2656,7 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PXLW</t>
+          <t>GTIM</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -3230,7 +2666,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PYPD</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -3240,7 +2676,7 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>GYRE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -3250,7 +2686,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RDNT</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -3260,7 +2696,7 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -3270,7 +2706,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -3280,7 +2716,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>RMNI</t>
+          <t>HELP</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -3290,7 +2726,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RNXT</t>
+          <t>HLNE</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -3300,7 +2736,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>HMR</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -3310,7 +2746,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>RRGB</t>
+          <t>HNNA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -3320,7 +2756,7 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>RUM</t>
+          <t>HNVR</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -3330,7 +2766,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RWAYI</t>
+          <t>HQWWW</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -3340,7 +2776,7 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>HRZN</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -3350,7 +2786,7 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SBMT</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -3360,7 +2796,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>HURC</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -3370,7 +2806,7 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SEGG</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -3380,7 +2816,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SENEA</t>
+          <t>HYPD</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -3390,7 +2826,7 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SFBC</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -3400,7 +2836,7 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SHC</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -3410,7 +2846,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SIEB</t>
+          <t>IDYA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -3420,7 +2856,7 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>IMMX</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -3430,7 +2866,7 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SLMBP</t>
+          <t>IMPP</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -3440,7 +2876,7 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SLP</t>
+          <t>IMRX</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -3450,7 +2886,7 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>IMUX</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -3460,7 +2896,7 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>INBKZ</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -3470,7 +2906,7 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>INBX</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -3480,7 +2916,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -3490,7 +2926,7 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>THH</t>
+          <t>INDI</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -3500,7 +2936,7 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>TLF</t>
+          <t>INFQ</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -3510,7 +2946,7 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>TPCS</t>
+          <t>INMB</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -3520,7 +2956,7 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>TRIN</t>
+          <t>INO</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -3530,7 +2966,7 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -3540,7 +2976,7 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>VACI</t>
+          <t>IPHA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -3550,7 +2986,7 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>IRD</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -3560,7 +2996,7 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>VERU</t>
+          <t>JAN</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -3570,7 +3006,7 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>VOXR</t>
+          <t>JANX</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -3580,7 +3016,7 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>VSECU</t>
+          <t>JCSE</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -3590,7 +3026,7 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>WSBCO</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -3600,7 +3036,7 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>WSTN</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -3610,11 +3046,1921 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>YORW</t>
+          <t>KELYA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>KIDZ</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>KLTR</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>KMDA</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>KOPN</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>KOYN</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>KPRX</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>KROS</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>KSPI</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>KWY</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>KZIA</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>LAUR</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>LEGH</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>LEXX</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>LGVN</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>LKQ</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>LKSP</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>LPBB</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>LYEL</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>MACI</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>MBINL</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>MBUU</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>MCGA</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>MDLZ</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>MEDP</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>MEOH</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>MFIN</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>MICC</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>MINE</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>MKTX</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>MLAA</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>MLAB</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>MMED</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>MMYT</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>MOLN</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr"/>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>MRX</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>MYSE</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>NAVI</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>NBP</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr"/>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>NCI</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr"/>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr"/>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr"/>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>NEGG</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>NEO</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr"/>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>NICM</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr"/>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>NIPG</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr"/>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>NIQ</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr"/>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>NMFCZ</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr"/>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>NPT</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr"/>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>NRC</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr"/>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>NTHI</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>NTNX</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>NTRA</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>NVAX</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>NVCT</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>NWS</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>NWSA</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr"/>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>NWTG</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>NXPL</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>OABI</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr"/>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>OBIO</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ODTX</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>OESX</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>OGC</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>OGG</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>OMER</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>OMEX</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>ONC</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>OPRT</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>ORBS</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>OXLCM</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>PAA</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>PAGP</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>PANL</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>PAX</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>PAYS</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr"/>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>PBAM</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr"/>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>PCVX</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr"/>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr"/>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>PEPG</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>PFSA</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>PFX</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr"/>
+      <c r="D321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>PHVS</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>PLSE</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr"/>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>PMN</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr"/>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>PMVP</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>PNRG</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr"/>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>PPC</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>PRAA</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr"/>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>PRAX</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr"/>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>PROV</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr"/>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>PRQR</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr"/>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>PRZO</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr"/>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>PSNL</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr"/>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>PTEN</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr"/>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>PURR</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>PXLW</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr"/>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>PXS</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr"/>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>PYPD</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr"/>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr"/>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>QQQX</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr"/>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>QURE</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr"/>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>RCBC</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr"/>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>RCMT</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr"/>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>RDZN</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>REAX</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>REFI</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr"/>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr"/>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>RENT</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>RGLD</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr"/>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>RILYG</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr"/>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>RMBI</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>RMCO</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr"/>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>RMNI</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr"/>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>RNAC</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>ROIV</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>ROKU</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr"/>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>RUM</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>RVMD</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr"/>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>RWAYI</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr"/>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>RXRX</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr"/>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>SAFT</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr"/>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>SAIH</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr"/>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SATA</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr"/>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>SBET</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr"/>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr"/>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SBMT</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr"/>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>SCWO</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr"/>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>SCYX</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr"/>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>SDGR</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr"/>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>SEIC</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr"/>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SHIP</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr"/>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr"/>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>SIBN</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr"/>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr"/>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>SLMBP</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr"/>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>SLNG</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr"/>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>SLP</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr"/>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>SLS</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr"/>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr"/>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SNY</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr"/>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr"/>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>SOPH</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr"/>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>SPCB</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr"/>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr"/>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>SPTX</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr"/>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>SQFTP</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr"/>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>SRTA</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr"/>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr"/>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>SSRM</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr"/>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr"/>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr"/>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>STRD</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr"/>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>STRF</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr"/>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr"/>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>SYRE</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr"/>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>TAYD</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>TECX</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr"/>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr"/>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>THH</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr"/>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>TILE</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr"/>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>TIPT</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr"/>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>TLF</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr"/>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>TOP</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr"/>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>TORO</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr"/>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr"/>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>TRLV</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr"/>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr"/>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr"/>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr"/>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>VERU</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr"/>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>VGNT</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr"/>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>VMET</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr"/>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>VOR</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr"/>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>VOXR</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr"/>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>VSECU</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr"/>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>WSBCO</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr"/>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>WSTN</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr"/>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>XNCR</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr"/>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>XXI</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr"/>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>ZSTK</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D288"/>
+  <dimension ref="A1:D297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADPT</t>
+          <t>ADAMK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEI</t>
+          <t>ADPT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>AEI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AIFA</t>
+          <t>AESP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AIRO</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AIXC</t>
+          <t>AIFA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALOT</t>
+          <t>AIRO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AIXC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>ALOT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>ALPX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ANGX</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ANL</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>APLM</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>APPF</t>
+          <t>ANGX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>ANL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AQST</t>
+          <t>APLM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>APPF</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARCC</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AREC</t>
+          <t>AQST</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ARX</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ASRV</t>
+          <t>ARCC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>AREC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATRA</t>
+          <t>ARX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>ASRV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AURA</t>
+          <t>ATKR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1090,13 +1090,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AUTL</t>
+          <t>ATRA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PRHIZ</t>
+          <t>PUSA</t>
         </is>
       </c>
     </row>
@@ -1108,13 +1108,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AVO</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PUSA</t>
+          <t>SHMD</t>
         </is>
       </c>
     </row>
@@ -1126,13 +1126,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>AURA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>SKHY</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AVR</t>
+          <t>AUTL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>AVO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BCDA</t>
+          <t>AVR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BEEP</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1225,12 +1225,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>BMNP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1239,12 +1239,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BNTX</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BGDE</t>
+          <t>BCDA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BPYPP</t>
+          <t>BNTX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>BEEP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1267,12 +1267,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BRNX</t>
+          <t>BPYPP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BNTC</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1281,12 +1281,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>BRNX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BOLD</t>
+          <t>BGDE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1295,12 +1295,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BTBD</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1309,12 +1309,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BTCS</t>
+          <t>BTBD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BPYPO</t>
+          <t>BNTC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1323,12 +1323,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BTGO</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BOLD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1337,12 +1337,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BULLW</t>
+          <t>BTGO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1351,12 +1351,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BWB</t>
+          <t>BULLW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BPYPO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1365,12 +1365,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>BWB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1379,12 +1379,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BTU</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1393,12 +1393,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CDLR</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BVC</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1407,12 +1407,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CDLR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1421,12 +1421,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CEPO</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BYND</t>
+          <t>BTU</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1435,12 +1435,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CGAU</t>
+          <t>CEPO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>BVC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1449,12 +1449,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>CGAU</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1463,12 +1463,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CHTRP</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BYND</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1477,12 +1477,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CING</t>
+          <t>CHTRP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CCG</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1491,12 +1491,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CITR</t>
+          <t>CING</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1505,12 +1505,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CITR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CELU</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1519,12 +1519,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CMMB</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CETY</t>
+          <t>CCG</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1533,12 +1533,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CMTV</t>
+          <t>CMMB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1547,12 +1547,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CNOBP</t>
+          <t>CMTV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>CELU</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1561,12 +1561,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CNR</t>
+          <t>CNOBP</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CLBK</t>
+          <t>CETY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1575,12 +1575,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>COCP</t>
+          <t>CNR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1589,12 +1589,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CRBP</t>
+          <t>COCP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>CHNR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1603,12 +1603,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CSHR</t>
+          <t>CRBP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>CLBK</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1617,12 +1617,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>CSHR</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1631,12 +1631,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>CSTL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1645,12 +1645,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CTRM</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CPB</t>
+          <t>CNET</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1659,12 +1659,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>CTRM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CPBI</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1673,12 +1673,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CYCN</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CRMD</t>
+          <t>CORT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1687,12 +1687,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>CYCN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1701,12 +1701,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>CPBI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1715,12 +1715,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>CYRX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CSAI</t>
+          <t>CRMD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1729,12 +1729,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CSWC</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1743,12 +1743,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DCH</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1757,12 +1757,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>DCH</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CSAI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1771,12 +1771,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CTW</t>
+          <t>CSWC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1785,12 +1785,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DHCNI</t>
+          <t>DFDV</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1799,12 +1799,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>DHCNI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DAAQ</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1813,12 +1813,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>DMAA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>CTW</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1827,12 +1827,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>CZNC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1841,12 +1841,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DRTS</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DERM</t>
+          <t>DAAQ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1855,12 +1855,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DRUG</t>
+          <t>DRTS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DFTX</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1869,12 +1869,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DSGN</t>
+          <t>DRUG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DTCX</t>
+          <t>DSGN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DNUT</t>
+          <t>DERM</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1897,12 +1897,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DTIL</t>
+          <t>DTCX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DUOT</t>
+          <t>DFTX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1911,12 +1911,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DWTX</t>
+          <t>DTIL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1925,12 +1925,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EDRY</t>
+          <t>DWTX</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ECCU</t>
+          <t>DNUT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1939,12 +1939,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ELBM</t>
+          <t>EDRY</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>DSC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1953,12 +1953,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ELLA</t>
+          <t>ELBM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EGHA</t>
+          <t>DUOT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1967,12 +1967,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>ELLA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ELE</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1981,12 +1981,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ELVN</t>
+          <t>ECCU</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1995,12 +1995,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EPRX</t>
+          <t>ELOX</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EROK</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2009,12 +2009,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>ENTX</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>EGHA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2023,12 +2023,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EXFY</t>
+          <t>ELE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2037,12 +2037,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>ELVN</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2051,12 +2051,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBLG</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>EROK</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2065,12 +2065,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBRX</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FDMT</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2079,12 +2079,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FHTX</t>
+          <t>FBLG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>EXFY</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2093,12 +2093,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>FBRX</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FENC</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2107,12 +2107,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>FHTX</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FERA</t>
+          <t>FCBC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2121,12 +2121,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FLNT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FIGR</t>
+          <t>FDMT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2135,12 +2135,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2149,12 +2149,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>FLNT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>FENC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2163,12 +2163,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>FERA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2177,12 +2177,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FTH</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FORR</t>
+          <t>FIGR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2191,12 +2191,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FUTU</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2205,12 +2205,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FVN</t>
+          <t>FTH</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FOXF</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2219,12 +2219,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>FUTU</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FRNM</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2233,12 +2233,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>FVN</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>FORR</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2247,12 +2247,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GECCI</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FWONA</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2261,12 +2261,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>GAINZ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FWONK</t>
+          <t>FOXF</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2275,12 +2275,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GOLD</t>
+          <t>GECCI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GAME</t>
+          <t>FRNM</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2289,12 +2289,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GYRE</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2303,12 +2303,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>GOLD</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>FWONA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2317,12 +2317,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HELP</t>
+          <t>GYRE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GECCG</t>
+          <t>FWONK</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2331,12 +2331,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HLXC</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>GAME</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2345,12 +2345,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>HOLO</t>
+          <t>HELP</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2359,12 +2359,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HQI</t>
+          <t>HLXC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GLBS</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2373,12 +2373,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>HOLO</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GMRS</t>
+          <t>GECCG</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2387,12 +2387,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>HYPD</t>
+          <t>HQI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2401,12 +2401,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2415,12 +2415,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>IDYA</t>
+          <t>HYPD</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>GLBS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2429,12 +2429,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GROW</t>
+          <t>GMRS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2443,12 +2443,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>IMPP</t>
+          <t>IDYA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GRRR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -2457,12 +2457,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>INFQ</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GRVY</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -2471,12 +2471,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>INMB</t>
+          <t>IMPP</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GSHD</t>
+          <t>GRAL</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -2485,12 +2485,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>INFQ</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GTEC</t>
+          <t>GROW</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2499,12 +2499,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>INMB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GTIM</t>
+          <t>GRRR</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2513,12 +2513,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>IVVD</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>GRVY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -2527,12 +2527,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JATT</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>GSHD</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -2541,12 +2541,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>JUNS</t>
+          <t>IVVD</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GTEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -2555,12 +2555,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>JATT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>HLNE</t>
+          <t>GTIM</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -2569,12 +2569,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>JUNS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HNST</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -2583,12 +2583,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>LGVN</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -2597,12 +2597,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>LOT</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HQWWW</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -2611,12 +2611,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>LGVN</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HRZN</t>
+          <t>HLNE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -2625,12 +2625,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>LOT</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>HNST</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -2639,12 +2639,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HUDI</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2653,12 +2653,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>MCAH</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HURC</t>
+          <t>HQWWW</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2667,12 +2667,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IACO</t>
+          <t>HRZN</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2681,12 +2681,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IMCR</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2695,12 +2695,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MRDN</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IMMX</t>
+          <t>HUDI</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2709,12 +2709,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IMUX</t>
+          <t>HURC</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2723,12 +2723,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSBIP</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>INBX</t>
+          <t>IACO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2737,12 +2737,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NAKA</t>
+          <t>MRDN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>INDI</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2751,12 +2751,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NBP</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>INO</t>
+          <t>IMCR</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2765,12 +2765,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NCI</t>
+          <t>MSBIP</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IPHA</t>
+          <t>IMMX</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2779,12 +2779,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>NAKA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JAN</t>
+          <t>IMUX</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2793,12 +2793,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NMFCZ</t>
+          <t>NBP</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>JFU</t>
+          <t>INBX</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2807,12 +2807,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NRC</t>
+          <t>NCI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>INDI</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2821,12 +2821,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>INO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2835,12 +2835,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NTRB</t>
+          <t>NMFCZ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>KELYA</t>
+          <t>IPHA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2849,12 +2849,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>NRC</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>JAN</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2863,12 +2863,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NVCT</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>KMDA</t>
+          <t>JFU</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2877,12 +2877,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ODTX</t>
+          <t>NTRB</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>KOPN</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2891,12 +2891,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OMEX</t>
+          <t>NVAX</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>KPRX</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2905,12 +2905,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ONBPO</t>
+          <t>NVCT</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>KRKR</t>
+          <t>KELYA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2919,12 +2919,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ORBS</t>
+          <t>OCAC</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>KRNY</t>
+          <t>KLTR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2933,12 +2933,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>OTLY</t>
+          <t>ODTX</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>KSPI</t>
+          <t>KMDA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2947,12 +2947,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>OVLY</t>
+          <t>OMEX</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>KWY</t>
+          <t>KOPN</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2961,12 +2961,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>ONBPO</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>KZIA</t>
+          <t>KPRX</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2975,12 +2975,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>ORBS</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>KRKR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2989,12 +2989,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PANL</t>
+          <t>OTLY</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LEGH</t>
+          <t>KRNY</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3003,12 +3003,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>OVLY</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LEXX</t>
+          <t>KSPI</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3017,12 +3017,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PEBK</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>KWY</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -3031,12 +3031,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>KZIA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -3045,12 +3045,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PFX</t>
+          <t>PANL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LPTH</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -3059,12 +3059,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LSE</t>
+          <t>LEGH</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3073,12 +3073,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>PBLS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>LEXX</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -3087,12 +3087,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PRZO</t>
+          <t>PEBK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MAKO</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -3101,12 +3101,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PSEC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>LMRI</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -3115,12 +3115,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PSNL</t>
+          <t>PFX</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MBINL</t>
+          <t>LPTH</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -3129,12 +3129,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>PHOS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MCFT</t>
+          <t>LSE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3143,12 +3143,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PURR</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>LTGO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -3157,12 +3157,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -3171,12 +3171,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PYPD</t>
+          <t>PRZO</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MGTX</t>
+          <t>MAKO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -3185,12 +3185,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RDI</t>
+          <t>PSEC</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MGYR</t>
+          <t>MASS</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -3199,12 +3199,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>REAX</t>
+          <t>PSNL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>MBINL</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -3213,12 +3213,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>REFI</t>
+          <t>PTLO</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MINE</t>
+          <t>MCFT</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -3227,12 +3227,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RENT</t>
+          <t>PURR</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -3241,12 +3241,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>PXS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MMED</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -3255,12 +3255,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>PYPD</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MNKD</t>
+          <t>MGTX</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -3269,12 +3269,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RMBI</t>
+          <t>RDI</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MNOV</t>
+          <t>MGYR</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -3283,12 +3283,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RMNI</t>
+          <t>REAX</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MOLN</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -3297,12 +3297,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RMR</t>
+          <t>REFI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MRX</t>
+          <t>MINE</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -3311,12 +3311,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RNAC</t>
+          <t>RENT</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -3325,12 +3325,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>RGEN</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MYSE</t>
+          <t>MMED</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -3339,12 +3339,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RVMD</t>
+          <t>RGLD</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MYSZ</t>
+          <t>MNKD</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -3353,12 +3353,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>RMBI</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>NAVI</t>
+          <t>MNOV</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -3367,12 +3367,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>RMNI</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>MOLN</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -3381,12 +3381,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>RMR</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NICM</t>
+          <t>MRX</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -3395,12 +3395,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SBMT</t>
+          <t>RNAC</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>NIPG</t>
+          <t>MTEX</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -3409,12 +3409,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>MYSE</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -3423,12 +3423,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SHIP</t>
+          <t>RVMD</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>NPAC</t>
+          <t>MYSZ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -3437,12 +3437,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>SATA</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>NAVI</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -3451,12 +3451,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>NTHI</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -3465,12 +3465,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SLS</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>NICM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -3479,12 +3479,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SMJF</t>
+          <t>SBMT</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>NIPG</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -3493,12 +3493,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SMTI</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -3507,12 +3507,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>SHIP</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>NPAC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -3521,12 +3521,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SRTA</t>
+          <t>SIBN</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>OABI</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -3535,12 +3535,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>SIND</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>OBIO</t>
+          <t>NTHI</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -3549,12 +3549,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SSRM</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>OCCI</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -3563,12 +3563,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>SLS</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>OCUL</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -3577,12 +3577,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STRD</t>
+          <t>SMJF</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -3591,12 +3591,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>SMTI</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>OGC</t>
+          <t>NXPL</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -3605,12 +3605,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>OGG</t>
+          <t>OABI</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -3619,12 +3619,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SYRE</t>
+          <t>SRTA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>OGI</t>
+          <t>OBIO</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -3633,12 +3633,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TAYD</t>
+          <t>SSMR</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>OMER</t>
+          <t>OCCI</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -3647,12 +3647,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TBPH</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>OMSE</t>
+          <t>OCUL</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -3661,12 +3661,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TCBX</t>
+          <t>SSRM</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>OXLCG</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -3675,12 +3675,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>OGC</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -3689,12 +3689,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TII</t>
+          <t>STRD</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>OGG</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -3703,12 +3703,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TOP</t>
+          <t>STRF</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PBAM</t>
+          <t>OGI</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -3717,12 +3717,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TRLV</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PBM</t>
+          <t>OMER</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -3731,12 +3731,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SYRE</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>OMSE</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -3745,12 +3745,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TRON</t>
+          <t>TAYD</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>OXLCG</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -3759,12 +3759,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>TBPH</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PHOE</t>
+          <t>OXLCM</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -3773,12 +3773,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>TWAV</t>
+          <t>TCBX</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PLSE</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -3787,12 +3787,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>VGNT</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PMN</t>
+          <t>PBAM</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -3801,12 +3801,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>VMET</t>
+          <t>TII</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PMTS</t>
+          <t>PBM</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -3815,12 +3815,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>VOXR</t>
+          <t>TOP</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PMTW</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -3829,132 +3829,180 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>XXI</t>
+          <t>TRLV</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PMVP</t>
+          <t>PEPG</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PPC</t>
+          <t>PHOE</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr"/>
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>TRON</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PRAA</t>
+          <t>PLSE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>PLUN</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr"/>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>TWAV</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>PMN</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr"/>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>USDE</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>PMTS</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr"/>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>USDEW</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PROV</t>
+          <t>PMTW</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr"/>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>VGNT</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PRPO</t>
+          <t>PMVP</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr"/>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>VMET</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PRQR</t>
+          <t>PPC</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr"/>
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>VOGX</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PRTA</t>
+          <t>PRAA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr"/>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>VOXR</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr"/>
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>WHK</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PSUS</t>
+          <t>PRHI</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr"/>
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>XXI</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PRLD</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -3964,7 +4012,7 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>PROV</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -3974,7 +4022,7 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>PRPO</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -3984,7 +4032,7 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>QTTB</t>
+          <t>PRQR</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -3994,7 +4042,7 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>RBKB</t>
+          <t>PRTA</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -4004,7 +4052,7 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -4014,7 +4062,7 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>PSUS</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -4024,7 +4072,7 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -4034,7 +4082,7 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>PTEN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -4044,7 +4092,7 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>QMCO</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -4054,7 +4102,7 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>RMCO</t>
+          <t>QTTB</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -4064,7 +4112,7 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>RMTI</t>
+          <t>RBKB</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -4074,7 +4122,7 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -4084,7 +4132,7 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -4094,7 +4142,7 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>RRGB</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -4104,7 +4152,7 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
-          <t>RUM</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -4114,7 +4162,7 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
-          <t>RWAYI</t>
+          <t>RILYG</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -4124,7 +4172,7 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>RMCO</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -4134,7 +4182,7 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>RMTI</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -4144,7 +4192,7 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SATL</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -4154,7 +4202,7 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SAV</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -4164,7 +4212,7 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>RRGB</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -4174,7 +4222,7 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>RUM</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -4184,7 +4232,7 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SENEA</t>
+          <t>RWAYI</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -4194,7 +4242,7 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>SHC</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -4204,7 +4252,7 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>SAIH</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -4214,7 +4262,7 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SLNG</t>
+          <t>SATL</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -4224,7 +4272,7 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SLP</t>
+          <t>SAV</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -4234,7 +4282,7 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -4244,7 +4292,7 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>SCTX</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -4254,7 +4302,7 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SOPH</t>
+          <t>SCYX</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -4264,7 +4312,7 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SPAI</t>
+          <t>SENEA</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -4274,7 +4322,7 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SPCB</t>
+          <t>SHC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -4284,7 +4332,7 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SPEG</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -4294,7 +4342,7 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>SLNG</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -4304,7 +4352,7 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SQFTP</t>
+          <t>SLP</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -4314,7 +4362,7 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>STEP</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -4324,7 +4372,7 @@
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>STRA</t>
+          <t>SMCIP</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -4334,7 +4382,7 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SUNC</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -4344,7 +4392,7 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>TECX</t>
+          <t>SOPH</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -4354,7 +4402,7 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SPAI</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -4364,7 +4412,7 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>SPCB</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -4374,7 +4422,7 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>TKNO</t>
+          <t>SPEG</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -4384,7 +4432,7 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>TLF</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -4394,7 +4442,7 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>SQFTP</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -4404,7 +4452,7 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>TORO</t>
+          <t>STEP</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -4414,7 +4462,7 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>TRIN</t>
+          <t>STRA</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -4424,7 +4472,7 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>SUNC</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -4434,7 +4482,7 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>VACI</t>
+          <t>TECX</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -4444,7 +4492,7 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>XNCR</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -4454,11 +4502,101 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>XRN</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>TKNO</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>TLF</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>TMDX</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>TORO</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>TRIN</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr"/>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>VACI</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>XNCR</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>XRN</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/momentum_strong_latest.xlsx
+++ b/results/momentum_strong_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D325"/>
+  <dimension ref="A1:D426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,2834 +441,2030 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABLV</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AARD</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ABAT</t>
-        </is>
-      </c>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AIRE</t>
+          <t>AD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>BRNX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACHV</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+          <t>ACET</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>AIDX</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ALCO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABTS</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACT</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AWRE</t>
-        </is>
-      </c>
+          <t>ACNB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AMST</t>
+          <t>ATOS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ACET</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACU</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>BMRA</t>
-        </is>
-      </c>
+          <t>ADAMK</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ATLX</t>
+          <t>CGTL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>NXPL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>ADBE</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ADAMH</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>BTBT</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BNKK</t>
+          <t>COYA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADPT</t>
+          <t>OCCIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADAMI</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BORR</t>
+          <t>DXST</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>QNRX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ADAMN</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ELUT</t>
-        </is>
-      </c>
+          <t>AEI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BSEM</t>
+          <t>ENGN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADUS</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADP</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ERNA</t>
-        </is>
-      </c>
+          <t>AERT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CGTL</t>
+          <t>FLD</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ADVB</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AESP</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FLD</t>
-        </is>
-      </c>
+          <t>AEYE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CNTN</t>
+          <t>FULC</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AFYA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GAUZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AGPU</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GFAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
         <is>
           <t>AGYS</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AEYE</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GSRV</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DLPN</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AIOS</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>AKTS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>HDRN</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>DUKR</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AIRT</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AIFA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>IMPP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AIFC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>IONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ALGS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>KLRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
         <is>
           <t>ALRM</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LBTYA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ELVR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
         <is>
           <t>AMPL</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ALT</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LBTYK</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>EVAX</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ANAB</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ALVO</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>PPIH</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>EZRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>APPF</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>AMCX</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SERA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FLUX</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>APPN</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SKYA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>FWRG</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ARCC</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LNZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
         <is>
           <t>AMR</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SRZN</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>GFAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ASST</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ANDG</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GRNQ</t>
+          <t>LUCD</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ATRC</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ANY</t>
+          <t>ANGO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GRRR</t>
+          <t>MFP</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AVTR</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ANGX</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IONS</t>
+          <t>MODD</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AXGN</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>APGE</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ISNR</t>
+          <t>NAMM</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AYA</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>APMC</t>
+          <t>APLM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LONA</t>
+          <t>OPTX</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BCCQ</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARCL</t>
+          <t>APPF</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OCGN</t>
+          <t>PPBT</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>BIII</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ARCT</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PAVM</t>
+          <t>QSI</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BL</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ARGX</t>
+          <t>APRE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>RECT</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>BLMN</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ASUR</t>
+          <t>AQST</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PMEC</t>
+          <t>RHLD</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>BMNR</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>SKHY</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>BPYPN</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AUGO</t>
+          <t>ARCC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>RECT</t>
+          <t>SLDP</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>BPYPO</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AURA</t>
+          <t>ARLP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RYM</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>BRCB</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>ARTNA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SKHY</t>
+          <t>WHK</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>BRNS</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AVBC</t>
+          <t>ARX</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>SPCX</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>BRNX</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ASBP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TLSA</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>BRZE</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AZTR</t>
+          <t>ASMB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>BSY</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BANX</t>
+          <t>ATAT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>BTU</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BGC</t>
+          <t>ATKR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>BULL</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>BUUU</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BIVI</t>
+          <t>AUGO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>BWBBP</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>AVBC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BLSH</t>
+          <t>AXGN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CCG</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BLSM</t>
+          <t>AYA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CCU</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BMEA</t>
+          <t>BANX</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>CDNA</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>BBNX</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>CELU</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BPYPM</t>
+          <t>BCRX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CGBD</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BEEP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>CHEC</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BTBD</t>
+          <t>BFRI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CHRD</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BTCS</t>
+          <t>BGC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>CMMB</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BTCT</t>
+          <t>BHFAO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>CNOBP</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BTGO</t>
+          <t>BIII</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>COUR</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BTLN</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>CRAI</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BTOC</t>
+          <t>BLSM</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>CSHR</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BULLW</t>
+          <t>BMEA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>CYPH</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BWIV</t>
+          <t>BMNP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>DBX</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>DCBO</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CABA</t>
+          <t>BPYPN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>DFDV</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CADL</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>DFDVW</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CARL</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>DOCU</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BRNS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>DOX</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>DSGX</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>ERIE</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>BSBK</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>EVER</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CDZI</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>FBLA</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CEG</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>FIVE</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>BTBD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>FNKO</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>FORR</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CG</t>
+          <t>BTGO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>FOX</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CGAU</t>
+          <t>BULL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>FROG</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CGEM</t>
+          <t>BULLW</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>FWDI</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CGON</t>
+          <t>BUUU</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>FWONA</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>BYND</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>GENB</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CHSCL</t>
+          <t>CACC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>GENVR</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>GLXY</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>CBAT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>GTLB</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>CBLL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>HBIO</t>
-        </is>
-      </c>
+      <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CLBK</t>
+          <t>CCCC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>HCM</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CNDT</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>HLNE</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>CDLR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>HNST</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CNR</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>HSDT</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>HURN</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COCP</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>HYPD</t>
-        </is>
-      </c>
+      <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>IBRX</t>
-        </is>
-      </c>
+      <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>IDAI</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>CG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>ILMN</t>
-        </is>
-      </c>
+      <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>COYA</t>
+          <t>CGAU</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>INTA</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CRBP</t>
+          <t>CGBD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>IPSC</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>CGEM</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>IVA</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CSWC</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>KARO</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CTNM</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>KELYA</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CLAR</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>KMB</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>CLBK</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>KRNY</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DAIC</t>
+          <t>CLLS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>KZIA</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DCBG</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>LASE</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DEFT</t>
+          <t>CMMB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>LEXX</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DERM</t>
+          <t>CNDT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>LHSW</t>
-        </is>
-      </c>
+      <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>CNSP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>LOT</t>
-        </is>
-      </c>
+      <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DNUT</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>LTGO</t>
-        </is>
-      </c>
+      <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DRMA</t>
+          <t>COCP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>MAZE</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DUOT</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>MBINM</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DWTX</t>
+          <t>CORT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>MDXG</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>COUR</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>MESO</t>
-        </is>
-      </c>
+      <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EDIT</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>METC</t>
-        </is>
-      </c>
+      <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>MNDY</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ELBM</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>MOLN</t>
-        </is>
-      </c>
+      <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ELLA</t>
+          <t>CRBP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>MORN</t>
-        </is>
-      </c>
+      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>CRNX</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>MRSH</t>
-        </is>
-      </c>
+      <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ELVN</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
+      <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>CSWC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>MSTR</t>
-        </is>
-      </c>
+      <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EML</t>
+          <t>CTNM</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>MTCH</t>
-        </is>
-      </c>
+      <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EPSN</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>NAVN</t>
-        </is>
-      </c>
+      <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>CWBC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>NBRGU</t>
-        </is>
-      </c>
+      <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>NBTX</t>
-        </is>
-      </c>
+      <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>NCNO</t>
-        </is>
-      </c>
+      <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>NEO</t>
-        </is>
-      </c>
+      <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>DERM</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>NGEN</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FBLG</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>NKTX</t>
-        </is>
-      </c>
+      <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>DHCNI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>NMFC</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FGII</t>
+          <t>DJCO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>NSIT</t>
-        </is>
-      </c>
+      <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>DMC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>NTNX</t>
-        </is>
-      </c>
+      <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>NVA</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>NWS</t>
-        </is>
-      </c>
+      <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FORTY</t>
+          <t>DSGN</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>NWSA</t>
-        </is>
-      </c>
+      <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>OESX</t>
-        </is>
-      </c>
+      <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>DUOL</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>OFS</t>
-        </is>
-      </c>
+      <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FSHP</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>OGI</t>
-        </is>
-      </c>
+      <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FSSL</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>OMDA</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FWONK</t>
+          <t>EDIT</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>OMSE</t>
-        </is>
-      </c>
+      <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>EDRY</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>ORMP</t>
-        </is>
-      </c>
+      <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GASS</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>OVID</t>
-        </is>
-      </c>
+      <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>ELBM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>PAHC</t>
-        </is>
-      </c>
+      <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>ELE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>PANL</t>
-        </is>
-      </c>
+      <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GEMI</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>PBLS</t>
-        </is>
-      </c>
+      <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>PCTY</t>
-        </is>
-      </c>
+      <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>EOLS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>PEGA</t>
-        </is>
-      </c>
+      <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GLBS</t>
+          <t>EROK</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
+      <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GLE</t>
+          <t>ESEA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>PMTW</t>
-        </is>
-      </c>
+      <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GLIBK</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>PRE</t>
-        </is>
-      </c>
+      <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GLSI</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>PRQR</t>
-        </is>
-      </c>
+      <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GMTL</t>
+          <t>EXEL</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>PSNYW</t>
-        </is>
-      </c>
+      <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GRI</t>
+          <t>EXFY</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>PSUS</t>
-        </is>
-      </c>
+      <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>GROW</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>PTEN</t>
-        </is>
-      </c>
+      <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GSHD</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>PTN</t>
-        </is>
-      </c>
+      <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GWRS</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>PURR</t>
-        </is>
-      </c>
+      <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>FCBC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>QNBC</t>
-        </is>
-      </c>
+      <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>FCFS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>RDI</t>
-        </is>
-      </c>
+      <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>HELP</t>
+          <t>FCNCO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>RDVT</t>
-        </is>
-      </c>
+      <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>HGBL</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>RILYG</t>
-        </is>
-      </c>
+      <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>HHS</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>RILYN</t>
-        </is>
-      </c>
+      <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>HMR</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>RILYZ</t>
-        </is>
-      </c>
+      <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HNRG</t>
+          <t>FORR</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>RMNI</t>
-        </is>
-      </c>
+      <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>ROKU</t>
-        </is>
-      </c>
+      <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>HQI</t>
+          <t>FRNM</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>ROP</t>
-        </is>
-      </c>
+      <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HRMY</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>RVMD</t>
-        </is>
-      </c>
+      <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HSCS</t>
+          <t>FSEA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>SABR</t>
-        </is>
-      </c>
+      <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HSLV</t>
+          <t>FSSL</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>SAGU</t>
-        </is>
-      </c>
+      <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>FTAIM</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>SAIC</t>
-        </is>
-      </c>
+      <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>IBEX</t>
+          <t>FVNNR</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>SAV</t>
-        </is>
-      </c>
+      <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>GAIN</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>SEIC</t>
-        </is>
-      </c>
+      <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>GALT</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
+      <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>GASS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>SIND</t>
-        </is>
-      </c>
+      <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>IKT</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>SLDB</t>
-        </is>
-      </c>
+      <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>IMMR</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>SLMBP</t>
-        </is>
-      </c>
+      <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>IMXI</t>
+          <t>GENK</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>SLS</t>
-        </is>
-      </c>
+      <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>GENVR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>SMCIP</t>
-        </is>
-      </c>
+      <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>INFQ</t>
+          <t>GEVO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>SOPH</t>
-        </is>
-      </c>
+      <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>IOND</t>
+          <t>GLAD</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
+      <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>IPWR</t>
+          <t>GLBS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>SRPT</t>
-        </is>
-      </c>
+      <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>IQMX</t>
+          <t>GLIBA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>SSNC</t>
-        </is>
-      </c>
+      <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>GLIBK</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>STDN</t>
-        </is>
-      </c>
+      <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>GLNG</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>STHO</t>
-        </is>
-      </c>
+      <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>KEQU</t>
+          <t>GOLD</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>STKE</t>
-        </is>
-      </c>
+      <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>KEYY</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>STRC</t>
-        </is>
-      </c>
+      <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>GRML</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>STRD</t>
-        </is>
-      </c>
+      <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>KIDZ</t>
+          <t>GRVY</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>STRF</t>
-        </is>
-      </c>
+      <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>KMDA</t>
+          <t>GSHD</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>TAOX</t>
-        </is>
-      </c>
+      <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>KRSP</t>
+          <t>GWAV</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>TARS</t>
-        </is>
-      </c>
+      <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>GWRS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>TAYD</t>
-        </is>
-      </c>
+      <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>KSPI</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>TEAM</t>
-        </is>
-      </c>
+      <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>KTTA</t>
+          <t>HBANL</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>TIL</t>
-        </is>
-      </c>
+      <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>KWY</t>
+          <t>HBANM</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>TRMD</t>
-        </is>
-      </c>
+      <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>TRNI</t>
-        </is>
-      </c>
+      <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LBRX</t>
+          <t>HCKT</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>USDE</t>
-        </is>
-      </c>
+      <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LEGH</t>
+          <t>HELE</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>USDEW</t>
-        </is>
-      </c>
+      <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>HELP</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>VCTR</t>
-        </is>
-      </c>
+      <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LIEN</t>
+          <t>HLNE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>VGNT</t>
-        </is>
-      </c>
+      <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>VIR</t>
-        </is>
-      </c>
+      <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>LILAP</t>
+          <t>HNST</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>WSE</t>
-        </is>
-      </c>
+      <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LIME</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -3278,7 +2474,7 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -3288,7 +2484,7 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LNSR</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -3298,7 +2494,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>HSLV</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -3308,7 +2504,7 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>LPSN</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -3318,7 +2514,7 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>LUCY</t>
+          <t>HYMC</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -3328,7 +2524,7 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -3338,7 +2534,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -3348,7 +2544,7 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>ICFI</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -3358,7 +2554,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MCGA</t>
+          <t>ICG</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -3368,7 +2564,7 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -3378,7 +2574,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MENS</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -3388,7 +2584,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>IMRN</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -3398,7 +2594,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MESH</t>
+          <t>INBX</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -3408,7 +2604,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MEVO</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -3418,7 +2614,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>INO</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -3428,7 +2624,7 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -3438,7 +2634,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MINE</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -3448,7 +2644,7 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>IOND</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -3458,7 +2654,7 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MNOV</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -3468,7 +2664,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MNSB</t>
+          <t>IPEX</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -3478,7 +2674,7 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MSBIP</t>
+          <t>IPHA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -3488,7 +2684,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>MYSZ</t>
+          <t>IPVV</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -3498,7 +2694,7 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>NAKA</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -3508,7 +2704,7 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>NAVI</t>
+          <t>ITIC</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -3518,7 +2714,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>IVVD</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -3528,7 +2724,7 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>NEOG</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -3538,7 +2734,7 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>NEOV</t>
+          <t>JANX</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -3548,7 +2744,7 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>NESR</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -3558,7 +2754,7 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>NEXM</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -3568,7 +2764,7 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>NGNE</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -3578,7 +2774,7 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>NHPBP</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -3588,7 +2784,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>NICM</t>
+          <t>KARO</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -3598,7 +2794,7 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>NMFCZ</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -3608,7 +2804,7 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>NSTS</t>
+          <t>KELYA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -3618,7 +2814,7 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -3628,7 +2824,7 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>NVCR</t>
+          <t>KINS</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -3638,7 +2834,7 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -3648,7 +2844,7 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>OCCI</t>
+          <t>KMDA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -3658,7 +2854,7 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>OCLTU</t>
+          <t>KRNY</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -3668,7 +2864,7 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>OGC</t>
+          <t>KSPI</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -3678,7 +2874,7 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ONBPO</t>
+          <t>KTTA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -3688,7 +2884,7 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ONCH</t>
+          <t>KWY</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -3698,7 +2894,7 @@
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ORBS</t>
+          <t>KYMR</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -3708,7 +2904,7 @@
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="inlineStr">
         <is>
-          <t>ORIO</t>
+          <t>KYNB</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -3718,7 +2914,7 @@
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="inlineStr">
         <is>
-          <t>OTLY</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -3728,7 +2924,7 @@
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="inlineStr">
         <is>
-          <t>OVBC</t>
+          <t>LBRX</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -3738,7 +2934,7 @@
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="inlineStr">
         <is>
-          <t>OXLC</t>
+          <t>LCLN</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -3748,7 +2944,7 @@
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PACH</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -3758,7 +2954,7 @@
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>LEGH</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -3768,7 +2964,7 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PBAM</t>
+          <t>LEXX</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -3778,7 +2974,7 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>LFST</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -3788,7 +2984,7 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PGY</t>
+          <t>LHSW</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -3798,7 +2994,7 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PLMK</t>
+          <t>LIEN</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -3808,7 +3004,7 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PNRG</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -3818,7 +3014,7 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PPHC</t>
+          <t>LMRI</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -3828,7 +3024,7 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PRAA</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -3838,7 +3034,7 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PRDO</t>
+          <t>LTGO</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -3848,7 +3044,7 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>LXEO</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -3858,7 +3054,7 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PROV</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -3868,7 +3064,7 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PRPO</t>
+          <t>MCHX</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -3878,7 +3074,7 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PSKY</t>
+          <t>MDXG</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -3888,7 +3084,7 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -3898,7 +3094,7 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PUSA</t>
+          <t>MENS</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -3908,7 +3104,7 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PYPD</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -3918,7 +3114,7 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>MEVO</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -3928,7 +3124,7 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
-          <t>QNCX</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -3938,7 +3134,7 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
-          <t>QRHC</t>
+          <t>MGTX</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -3948,7 +3144,7 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
-          <t>QTTB</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -3958,7 +3154,7 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>RACD</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -3968,7 +3164,7 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>RCKT</t>
+          <t>MNDY</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -3978,7 +3174,7 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>REFI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -3988,7 +3184,7 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>REGCO</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -3998,7 +3194,7 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>REGCP</t>
+          <t>MTVA</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -4008,7 +3204,7 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>RENX</t>
+          <t>MWYN</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -4018,7 +3214,7 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>MYSE</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -4028,7 +3224,7 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>MYSZ</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -4038,7 +3234,7 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>NAKA</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -4048,7 +3244,7 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>RHLD</t>
+          <t>NAVI</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -4058,7 +3254,7 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>NCNO</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -4068,7 +3264,7 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>RIVN</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -4078,7 +3274,7 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>RLYB</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -4088,7 +3284,7 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>RMCO</t>
+          <t>NESR</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -4098,7 +3294,7 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>NGEN</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -4108,7 +3304,7 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>RWAY</t>
+          <t>NGNE</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -4118,7 +3314,7 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>RWAYI</t>
+          <t>NHPAP</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -4128,7 +3324,7 @@
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>RYOJ</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -4138,7 +3334,7 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>NICM</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -4148,7 +3344,7 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -4158,7 +3354,7 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>NKTX</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -4168,7 +3364,7 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>NMFC</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -4178,7 +3374,7 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>NMFCZ</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -4188,7 +3384,7 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SBMT</t>
+          <t>NRC</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -4198,7 +3394,7 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>NRDS</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -4208,7 +3404,7 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SCWO</t>
+          <t>NSAIU</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -4218,7 +3414,7 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SCZM</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -4228,7 +3424,7 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>NTLA</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -4238,7 +3434,7 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>SENEA</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -4248,7 +3444,7 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>NTRSO</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -4258,7 +3454,7 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>SGML</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -4268,7 +3464,7 @@
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>NVA</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -4278,7 +3474,7 @@
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>SHOT</t>
+          <t>NVCT</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -4288,7 +3484,7 @@
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>NWGL</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -4298,7 +3494,7 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SLN</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -4308,7 +3504,7 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>SLP</t>
+          <t>OCCI</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -4318,7 +3514,7 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>OFS</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -4328,7 +3524,7 @@
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>OGI</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -4338,7 +3534,7 @@
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>SRTS</t>
+          <t>OMDA</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -4348,7 +3544,7 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>SSMR</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -4358,7 +3554,7 @@
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>STEP</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -4368,7 +3564,7 @@
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>STOK</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -4378,7 +3574,7 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>STRZ</t>
+          <t>ORBS</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -4388,7 +3584,7 @@
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>STTK</t>
+          <t>ORIO</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -4398,7 +3594,7 @@
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>SUNC</t>
+          <t>ORMP</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -4408,7 +3604,7 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>OVBC</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -4418,7 +3614,7 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>SY</t>
+          <t>OVLY</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -4428,7 +3624,7 @@
       <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
-          <t>TASK</t>
+          <t>OXLC</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
@@ -4438,7 +3634,7 @@
       <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
-          <t>TCBIO</t>
+          <t>PAHC</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -4448,7 +3644,7 @@
       <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>PANL</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -4458,7 +3654,7 @@
       <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -4468,7 +3664,7 @@
       <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
-          <t>TGTX</t>
+          <t>PBM</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -4478,7 +3674,7 @@
       <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
-          <t>TII</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -4488,7 +3684,7 @@
       <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
-          <t>TJGC</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -4498,7 +3694,7 @@
       <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
-          <t>TLF</t>
+          <t>PEPG</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
@@ -4508,7 +3704,7 @@
       <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
-          <t>TMC</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -4518,7 +3714,7 @@
       <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
-          <t>TOP</t>
+          <t>PMTS</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
@@ -4528,7 +3724,7 @@
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>PPC</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -4538,7 +3734,7 @@
       <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>PPHC</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -4548,7 +3744,7 @@
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -4558,7 +3754,7 @@
       <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>PRAA</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -4568,7 +3764,7 @@
       <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
-          <t>USAU</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -4578,7 +3774,7 @@
       <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
-          <t>VOGX</t>
+          <t>PRDO</t>
         </is>
       </c>
       <c r="C320" t="inlineStr"/>
@@ -4588,7 +3784,7 @@
       <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -4598,7 +3794,7 @@
       <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>PROK</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -4608,7 +3804,7 @@
       <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
-          <t>XMAX</t>
+          <t>PROV</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -4618,7 +3814,7 @@
       <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
-          <t>XRN</t>
+          <t>PRTA</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -4628,11 +3824,1021 @@
       <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
-          <t>XZO</t>
+          <t>PRZO</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>PSEC</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr"/>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>PSUS</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>PTEN</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr"/>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>PURR</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>PXLW</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr"/>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>PYXS</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr"/>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>QNBC</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr"/>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>QNCX</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr"/>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>RANI</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>RAPP</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>RCEL</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr"/>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>RCMT</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr"/>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>RDVT</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>RDZN</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr"/>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>REFI</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr"/>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>RELY</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr"/>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>RENX</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr"/>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>RGLD</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr"/>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>RILYG</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr"/>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>RILYN</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr"/>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>RMBI</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>RMNI</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr"/>
+      <c r="D347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr"/>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>RMTI</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>RNAC</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>RNXT</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr"/>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>ROP</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr"/>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>RPC</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>RUM</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr"/>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>RWAY</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr"/>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>RZLV</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>SABR</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr"/>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>SAIC</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr"/>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>SAV</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>SBAC</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr"/>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>SBFG</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr"/>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>SBMT</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr"/>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>SCWO</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr"/>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>SCZM</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr"/>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>SEGG</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr"/>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SEIC</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr"/>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>SENEA</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr"/>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>SGHT</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr"/>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SGML</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr"/>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>SHIM</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr"/>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>SHIP</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr"/>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr"/>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr"/>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SLMBP</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr"/>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>SLN</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr"/>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>SLNG</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr"/>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>SLNHP</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr"/>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>SMCIP</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr"/>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>SPCX</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr"/>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>SPSC</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr"/>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr"/>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>SRPT</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr"/>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SRRK</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr"/>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>SSMR</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr"/>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr"/>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr"/>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>STOK</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr"/>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>STRA</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr"/>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr"/>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>STRF</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr"/>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr"/>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>STTK</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr"/>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>SUNC</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr"/>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>SVRN</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr"/>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>SWKHL</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr"/>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>SWVL</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr"/>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>SY</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr"/>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>TBPH</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr"/>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>TII</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>TJGC</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr"/>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>TMC</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr"/>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>TMCI</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr"/>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>TONT</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr"/>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>TOP</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr"/>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>TORO</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr"/>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>TPCS</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr"/>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>TPG</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr"/>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr"/>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>TRIN</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr"/>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr"/>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>TRNZ</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr"/>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>TRON</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr"/>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>USAR</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr"/>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>USAU</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr"/>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>USDE</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr"/>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>VCTR</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr"/>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>VGNT</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr"/>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>VIR</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr"/>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>VOXR</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr"/>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>VSNT</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr"/>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>WW</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr"/>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>XMAX</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr"/>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>XRN</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr"/>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>ZSTK</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
